--- a/data/Minimum_Assessor_Data.xlsx
+++ b/data/Minimum_Assessor_Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f3ac2bf50d090347/Documents/Python/Neontribe/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/F3AC2BF50D090347/Documents/Python/Neontribe/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:11_{37A86354-58CC-4CAD-94CF-10D12DAFBE26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:11_{37A86354-58CC-4CAD-94CF-10D12DAFBE26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F10477E5-11F8-4F97-ABAC-0F27AF87A313}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{618B0539-A1B0-495B-B98C-8ABAAC5394CB}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>ID</t>
   </si>
@@ -37,85 +37,10 @@
     <t>Scholarship type able to assess for</t>
   </si>
   <si>
-    <t>Jonathan Rivera</t>
+    <t>If able to assess Maths Masters, what is specialism?</t>
   </si>
   <si>
-    <t>jonathan.rivera@gmail.com</t>
-  </si>
-  <si>
-    <t>Tuesday 4 November (London); Monday 3 November (London)</t>
-  </si>
-  <si>
-    <t>Engineering Masters; Engineering PhD</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Sarah Young</t>
-  </si>
-  <si>
-    <t>sarah.young@academic.ac.uk</t>
-  </si>
-  <si>
-    <t>Monday 3 November (London); Monday 10 November (Birmingham); Tuesday 4 November (London)</t>
-  </si>
-  <si>
-    <t>AI PhD</t>
-  </si>
-  <si>
-    <t>Megan Baker</t>
-  </si>
-  <si>
-    <t>megan.baker@university.ac.uk</t>
-  </si>
-  <si>
-    <t>Monday 3 November (London); Tuesday 4 November (London); Thursday 6 November (Manchester)</t>
-  </si>
-  <si>
-    <t>Maths Masters; AI Masters; AI PhD</t>
-  </si>
-  <si>
-    <t>Theoretical Physics</t>
-  </si>
-  <si>
-    <t>Karen Young</t>
-  </si>
-  <si>
-    <t>karen.young@institution.edu</t>
-  </si>
-  <si>
-    <t>Monday 10 November (Birmingham); Thursday 6 November (Manchester)</t>
-  </si>
-  <si>
-    <t>AI Masters</t>
-  </si>
-  <si>
-    <t>Sophie Thomas</t>
-  </si>
-  <si>
-    <t>sophie.thomas@academic.ac.uk</t>
-  </si>
-  <si>
-    <t>Thursday 6 November (Manchester); Monday 10 November (Birmingham)</t>
-  </si>
-  <si>
-    <t>AI Masters; Maths PhD; Data Science Masters; Data Science PhD</t>
-  </si>
-  <si>
-    <t>Logic and set theory</t>
-  </si>
-  <si>
-    <t>Steven Jones</t>
-  </si>
-  <si>
-    <t>steven.jones@academic.ac.uk</t>
-  </si>
-  <si>
-    <t>If able to assess Maths , what is specialism?</t>
-  </si>
-  <si>
-    <t>if able to assess maths phd, what is specialism?</t>
+    <t>if able to assess Maths Phd, what is specialism?</t>
   </si>
 </sst>
 </file>
@@ -976,168 +901,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33005180-587A-445D-8D8E-272EE65B8088}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1">
-        <v>1</v>
-      </c>
-      <c r="C1">
-        <v>2</v>
-      </c>
-      <c r="D1">
-        <v>3</v>
-      </c>
-      <c r="E1">
-        <v>4</v>
-      </c>
-      <c r="F1">
-        <v>5</v>
-      </c>
-      <c r="G1">
-        <v>6</v>
-      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" t="s">
-        <v>28</v>
-      </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" t="s">
-        <v>29</v>
-      </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" t="s">
-        <v>16</v>
-      </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" t="s">
-        <v>8</v>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
